--- a/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
+++ b/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>GDPR Art 9 Exceptions</t>
+    <t>GDPR Article 9 Exception CodeSystem</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codes representing exceptions for processing special categories of personal data according to GDPR Article 9.</t>
+    <t>Code system defining GDPR Article 9 exceptions relevant for documenting the processing context of special categories of personal data, including health data.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>6</t>
   </si>
   <si>
     <t>Level</t>
@@ -139,6 +139,18 @@
   </si>
   <si>
     <t>Explicit Consent (Art. 9(2)(a))</t>
+  </si>
+  <si>
+    <t>gdpr-art-9-2-c</t>
+  </si>
+  <si>
+    <t>Vital Interests (Art. 9(2)(c))</t>
+  </si>
+  <si>
+    <t>gdpr-art-9-2-g</t>
+  </si>
+  <si>
+    <t>Substantial Public Interest (Art. 9(2)(g))</t>
   </si>
   <si>
     <t>gdpr-art-9-2-h</t>
@@ -458,7 +470,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -523,6 +535,30 @@
       </c>
       <c r="D5" s="2"/>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
+++ b/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>GDPR Article 9 Exception CodeSystem</t>
+    <t>GDPR Article 9 Condition Code System</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Code system defining GDPR Article 9 exceptions relevant for documenting the processing context of special categories of personal data, including health data.</t>
+    <t>Codes representing selected conditions in Article 9(2) GDPR under which special categories of personal data may be processed.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -141,34 +141,52 @@
     <t>Explicit Consent (Art. 9(2)(a))</t>
   </si>
   <si>
+    <t>The data subject has given explicit consent to the processing for one or more specified purposes, subject to applicable legal limitations.</t>
+  </si>
+  <si>
     <t>gdpr-art-9-2-c</t>
   </si>
   <si>
     <t>Vital Interests (Art. 9(2)(c))</t>
   </si>
   <si>
+    <t>Processing is necessary to protect vital interests where the data subject is physically or legally incapable of giving consent.</t>
+  </si>
+  <si>
     <t>gdpr-art-9-2-g</t>
   </si>
   <si>
     <t>Substantial Public Interest (Art. 9(2)(g))</t>
   </si>
   <si>
+    <t>Processing is necessary for reasons of substantial public interest on the basis of Union or Member State law and subject to appropriate safeguards.</t>
+  </si>
+  <si>
     <t>gdpr-art-9-2-h</t>
   </si>
   <si>
     <t>Health or Social Care (Art. 9(2)(h))</t>
   </si>
   <si>
+    <t>Processing is necessary for preventive or occupational medicine, medical diagnosis, provision or management of health or social care, or related systems and services, subject to the applicable legal conditions.</t>
+  </si>
+  <si>
     <t>gdpr-art-9-2-i</t>
   </si>
   <si>
     <t>Public Health (Art. 9(2)(i))</t>
   </si>
   <si>
+    <t>Processing is necessary for reasons of public interest in the area of public health on the basis of Union or Member State law and subject to appropriate safeguards.</t>
+  </si>
+  <si>
     <t>gdpr-art-9-2-j</t>
   </si>
   <si>
-    <t>Research (Art. 9(2)(j))</t>
+    <t>Research and Statistics (Art. 9(2)(j))</t>
+  </si>
+  <si>
+    <t>Processing is necessary for archiving in the public interest, scientific or historical research, or statistical purposes, subject to Article 89(1) GDPR and an applicable legal basis.</t>
   </si>
 </sst>
 </file>
@@ -497,67 +515,79 @@
       <c r="C2" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
+++ b/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
+++ b/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
+++ b/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
+++ b/r5-aist-trustworthyai-main/CodeSystem-gdpr-art9-codesystem.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/CodeSystem/gdpr-art9-codesystem</t>
+    <t>http://example.org/fhir/trust-ai-transparency/CodeSystem/gdpr-art9-codesystem</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:39:53+00:00</t>
+    <t>2026-09-09T11:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
